--- a/tests/test_dataset/files/fileA.xlsx
+++ b/tests/test_dataset/files/fileA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\llenezet\repositories\Files2DB\tests\test_dataset\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6014EEF1-7A05-4D02-88FD-B7F72AEB8C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A312ADCF-FF70-4489-882A-26B53837A34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{959416BF-3F10-4B98-A81C-92EDEEB58502}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="7">
   <si>
     <t>ColA</t>
   </si>
@@ -48,13 +48,7 @@
     <t>ColD</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
     <t>G</t>
-  </si>
-  <si>
-    <t>H</t>
   </si>
   <si>
     <t>ToSkip</t>
@@ -417,24 +411,24 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
@@ -446,29 +440,29 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -476,45 +470,43 @@
       <c r="D5" t="s">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
-        <v>4</v>
-      </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="E6" t="str">
+        <f>"2020-02-03"</f>
+        <v>2020-02-03</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
